--- a/esempi/Turni_PROVA_quattro_turni.xlsx
+++ b/esempi/Turni_PROVA_quattro_turni.xlsx
@@ -966,7 +966,6 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C4:$K4&lt;&gt;"")*(COUNTIFS($C4:$K4,$C4:$K4,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N4" s="5" t="str">
         <f aca="false">IF(LEN(AT4&amp;AU4&amp;AV4&amp;AW4&amp;AX4&amp;AY4)=0,"",LEFT(AT4&amp;AU4&amp;AV4&amp;AW4&amp;AX4&amp;AY4,LEN(AT4&amp;AU4&amp;AV4&amp;AW4&amp;AX4&amp;AY4)-2))</f>
@@ -1099,7 +1098,6 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C5:$K5&lt;&gt;"")*(COUNTIFS($C5:$K5,$C5:$K5,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N5" s="5" t="str">
         <f aca="false">IF(LEN(AT5&amp;AU5&amp;AV5&amp;AW5&amp;AX5&amp;AY5)=0,"",LEFT(AT5&amp;AU5&amp;AV5&amp;AW5&amp;AX5&amp;AY5,LEN(AT5&amp;AU5&amp;AV5&amp;AW5&amp;AX5&amp;AY5)-2))</f>
@@ -1232,7 +1230,6 @@
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C6:$K6&lt;&gt;"")*(COUNTIFS($C6:$K6,$C6:$K6,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N6" s="5" t="str">
         <f aca="false">IF(LEN(AT6&amp;AU6&amp;AV6&amp;AW6&amp;AX6&amp;AY6)=0,"",LEFT(AT6&amp;AU6&amp;AV6&amp;AW6&amp;AX6&amp;AY6,LEN(AT6&amp;AU6&amp;AV6&amp;AW6&amp;AX6&amp;AY6)-2))</f>
@@ -1365,7 +1362,6 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C7:$K7&lt;&gt;"")*(COUNTIFS($C7:$K7,$C7:$K7,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N7" s="5" t="str">
         <f aca="false">IF(LEN(AT7&amp;AU7&amp;AV7&amp;AW7&amp;AX7&amp;AY7)=0,"",LEFT(AT7&amp;AU7&amp;AV7&amp;AW7&amp;AX7&amp;AY7,LEN(AT7&amp;AU7&amp;AV7&amp;AW7&amp;AX7&amp;AY7)-2))</f>
@@ -1498,7 +1494,6 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C8:$K8&lt;&gt;"")*(COUNTIFS($C8:$K8,$C8:$K8,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N8" s="5" t="str">
         <f aca="false">IF(LEN(AT8&amp;AU8&amp;AV8&amp;AW8&amp;AX8&amp;AY8)=0,"",LEFT(AT8&amp;AU8&amp;AV8&amp;AW8&amp;AX8&amp;AY8,LEN(AT8&amp;AU8&amp;AV8&amp;AW8&amp;AX8&amp;AY8)-2))</f>
@@ -1631,7 +1626,6 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C9:$K9&lt;&gt;"")*(COUNTIFS($C9:$K9,$C9:$K9,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N9" s="11" t="str">
         <f aca="false">IF(LEN(AT9&amp;AU9&amp;AV9&amp;AW9&amp;AX9&amp;AY9)=0,"",LEFT(AT9&amp;AU9&amp;AV9&amp;AW9&amp;AX9&amp;AY9,LEN(AT9&amp;AU9&amp;AV9&amp;AW9&amp;AX9&amp;AY9)-2))</f>
@@ -1764,7 +1758,6 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C10:$K10&lt;&gt;"")*(COUNTIFS($C10:$K10,$C10:$K10,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N10" s="11" t="str">
         <f aca="false">IF(LEN(AT10&amp;AU10&amp;AV10&amp;AW10&amp;AX10&amp;AY10)=0,"",LEFT(AT10&amp;AU10&amp;AV10&amp;AW10&amp;AX10&amp;AY10,LEN(AT10&amp;AU10&amp;AV10&amp;AW10&amp;AX10&amp;AY10)-2))</f>
@@ -1910,7 +1903,6 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C11:$K11&lt;&gt;"")*(COUNTIFS($C11:$K11,$C11:$K11,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N11" s="5" t="str">
         <f aca="false">IF(LEN(AT11&amp;AU11&amp;AV11&amp;AW11&amp;AX11&amp;AY11)=0,"",LEFT(AT11&amp;AU11&amp;AV11&amp;AW11&amp;AX11&amp;AY11,LEN(AT11&amp;AU11&amp;AV11&amp;AW11&amp;AX11&amp;AY11)-2))</f>
@@ -2004,7 +1996,6 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C12:$K12&lt;&gt;"")*(COUNTIFS($C12:$K12,$C12:$K12,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N12" s="5" t="str">
         <f aca="false">IF(LEN(AT12&amp;AU12&amp;AV12&amp;AW12&amp;AX12&amp;AY12)=0,"",LEFT(AT12&amp;AU12&amp;AV12&amp;AW12&amp;AX12&amp;AY12,LEN(AT12&amp;AU12&amp;AV12&amp;AW12&amp;AX12&amp;AY12)-2))</f>
@@ -2101,7 +2092,6 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C13:$K13&lt;&gt;"")*(COUNTIFS($C13:$K13,$C13:$K13,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N13" s="5" t="str">
         <f aca="false">IF(LEN(AT13&amp;AU13&amp;AV13&amp;AW13&amp;AX13&amp;AY13)=0,"",LEFT(AT13&amp;AU13&amp;AV13&amp;AW13&amp;AX13&amp;AY13,LEN(AT13&amp;AU13&amp;AV13&amp;AW13&amp;AX13&amp;AY13)-2))</f>
@@ -2195,7 +2185,6 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C14:$K14&lt;&gt;"")*(COUNTIFS($C14:$K14,$C14:$K14,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N14" s="5" t="str">
         <f aca="false">IF(LEN(AT14&amp;AU14&amp;AV14&amp;AW14&amp;AX14&amp;AY14)=0,"",LEFT(AT14&amp;AU14&amp;AV14&amp;AW14&amp;AX14&amp;AY14,LEN(AT14&amp;AU14&amp;AV14&amp;AW14&amp;AX14&amp;AY14)-2))</f>
@@ -2289,7 +2278,6 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C15:$K15&lt;&gt;"")*(COUNTIFS($C15:$K15,$C15:$K15,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N15" s="5" t="str">
         <f aca="false">IF(LEN(AT15&amp;AU15&amp;AV15&amp;AW15&amp;AX15&amp;AY15)=0,"",LEFT(AT15&amp;AU15&amp;AV15&amp;AW15&amp;AX15&amp;AY15,LEN(AT15&amp;AU15&amp;AV15&amp;AW15&amp;AX15&amp;AY15)-2))</f>
@@ -2383,7 +2371,6 @@
       <c r="L16" s="11"/>
       <c r="M16" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C16:$K16&lt;&gt;"")*(COUNTIFS($C16:$K16,$C16:$K16,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N16" s="11" t="str">
         <f aca="false">IF(LEN(AT16&amp;AU16&amp;AV16&amp;AW16&amp;AX16&amp;AY16)=0,"",LEFT(AT16&amp;AU16&amp;AV16&amp;AW16&amp;AX16&amp;AY16,LEN(AT16&amp;AU16&amp;AV16&amp;AW16&amp;AX16&amp;AY16)-2))</f>
@@ -2477,7 +2464,6 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C17:$K17&lt;&gt;"")*(COUNTIFS($C17:$K17,$C17:$K17,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N17" s="11" t="str">
         <f aca="false">IF(LEN(AT17&amp;AU17&amp;AV17&amp;AW17&amp;AX17&amp;AY17)=0,"",LEFT(AT17&amp;AU17&amp;AV17&amp;AW17&amp;AX17&amp;AY17,LEN(AT17&amp;AU17&amp;AV17&amp;AW17&amp;AX17&amp;AY17)-2))</f>
@@ -2571,7 +2557,6 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C18:$K18&lt;&gt;"")*(COUNTIFS($C18:$K18,$C18:$K18,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N18" s="5" t="str">
         <f aca="false">IF(LEN(AT18&amp;AU18&amp;AV18&amp;AW18&amp;AX18&amp;AY18)=0,"",LEFT(AT18&amp;AU18&amp;AV18&amp;AW18&amp;AX18&amp;AY18,LEN(AT18&amp;AU18&amp;AV18&amp;AW18&amp;AX18&amp;AY18)-2))</f>
@@ -2665,7 +2650,6 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C19:$K19&lt;&gt;"")*(COUNTIFS($C19:$K19,$C19:$K19,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N19" s="5" t="str">
         <f aca="false">IF(LEN(AT19&amp;AU19&amp;AV19&amp;AW19&amp;AX19&amp;AY19)=0,"",LEFT(AT19&amp;AU19&amp;AV19&amp;AW19&amp;AX19&amp;AY19,LEN(AT19&amp;AU19&amp;AV19&amp;AW19&amp;AX19&amp;AY19)-2))</f>
@@ -2759,7 +2743,6 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C20:$K20&lt;&gt;"")*(COUNTIFS($C20:$K20,$C20:$K20,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N20" s="5" t="str">
         <f aca="false">IF(LEN(AT20&amp;AU20&amp;AV20&amp;AW20&amp;AX20&amp;AY20)=0,"",LEFT(AT20&amp;AU20&amp;AV20&amp;AW20&amp;AX20&amp;AY20,LEN(AT20&amp;AU20&amp;AV20&amp;AW20&amp;AX20&amp;AY20)-2))</f>
@@ -2853,7 +2836,6 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C21:$K21&lt;&gt;"")*(COUNTIFS($C21:$K21,$C21:$K21,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N21" s="5" t="str">
         <f aca="false">IF(LEN(AT21&amp;AU21&amp;AV21&amp;AW21&amp;AX21&amp;AY21)=0,"",LEFT(AT21&amp;AU21&amp;AV21&amp;AW21&amp;AX21&amp;AY21,LEN(AT21&amp;AU21&amp;AV21&amp;AW21&amp;AX21&amp;AY21)-2))</f>
@@ -2947,7 +2929,6 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C22:$K22&lt;&gt;"")*(COUNTIFS($C22:$K22,$C22:$K22,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N22" s="5" t="str">
         <f aca="false">IF(LEN(AT22&amp;AU22&amp;AV22&amp;AW22&amp;AX22&amp;AY22)=0,"",LEFT(AT22&amp;AU22&amp;AV22&amp;AW22&amp;AX22&amp;AY22,LEN(AT22&amp;AU22&amp;AV22&amp;AW22&amp;AX22&amp;AY22)-2))</f>
@@ -3041,7 +3022,6 @@
       <c r="L23" s="11"/>
       <c r="M23" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C23:$K23&lt;&gt;"")*(COUNTIFS($C23:$K23,$C23:$K23,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N23" s="11" t="str">
         <f aca="false">IF(LEN(AT23&amp;AU23&amp;AV23&amp;AW23&amp;AX23&amp;AY23)=0,"",LEFT(AT23&amp;AU23&amp;AV23&amp;AW23&amp;AX23&amp;AY23,LEN(AT23&amp;AU23&amp;AV23&amp;AW23&amp;AX23&amp;AY23)-2))</f>
@@ -3135,7 +3115,6 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C24:$K24&lt;&gt;"")*(COUNTIFS($C24:$K24,$C24:$K24,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N24" s="11" t="str">
         <f aca="false">IF(LEN(AT24&amp;AU24&amp;AV24&amp;AW24&amp;AX24&amp;AY24)=0,"",LEFT(AT24&amp;AU24&amp;AV24&amp;AW24&amp;AX24&amp;AY24,LEN(AT24&amp;AU24&amp;AV24&amp;AW24&amp;AX24&amp;AY24)-2))</f>
@@ -3229,7 +3208,6 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C25:$K25&lt;&gt;"")*(COUNTIFS($C25:$K25,$C25:$K25,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N25" s="5" t="str">
         <f aca="false">IF(LEN(AT25&amp;AU25&amp;AV25&amp;AW25&amp;AX25&amp;AY25)=0,"",LEFT(AT25&amp;AU25&amp;AV25&amp;AW25&amp;AX25&amp;AY25,LEN(AT25&amp;AU25&amp;AV25&amp;AW25&amp;AX25&amp;AY25)-2))</f>
@@ -3323,7 +3301,6 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C26:$K26&lt;&gt;"")*(COUNTIFS($C26:$K26,$C26:$K26,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N26" s="5" t="str">
         <f aca="false">IF(LEN(AT26&amp;AU26&amp;AV26&amp;AW26&amp;AX26&amp;AY26)=0,"",LEFT(AT26&amp;AU26&amp;AV26&amp;AW26&amp;AX26&amp;AY26,LEN(AT26&amp;AU26&amp;AV26&amp;AW26&amp;AX26&amp;AY26)-2))</f>
@@ -3417,7 +3394,6 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C27:$K27&lt;&gt;"")*(COUNTIFS($C27:$K27,$C27:$K27,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N27" s="5" t="str">
         <f aca="false">IF(LEN(AT27&amp;AU27&amp;AV27&amp;AW27&amp;AX27&amp;AY27)=0,"",LEFT(AT27&amp;AU27&amp;AV27&amp;AW27&amp;AX27&amp;AY27,LEN(AT27&amp;AU27&amp;AV27&amp;AW27&amp;AX27&amp;AY27)-2))</f>
@@ -3511,7 +3487,6 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C28:$K28&lt;&gt;"")*(COUNTIFS($C28:$K28,$C28:$K28,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N28" s="5" t="str">
         <f aca="false">IF(LEN(AT28&amp;AU28&amp;AV28&amp;AW28&amp;AX28&amp;AY28)=0,"",LEFT(AT28&amp;AU28&amp;AV28&amp;AW28&amp;AX28&amp;AY28,LEN(AT28&amp;AU28&amp;AV28&amp;AW28&amp;AX28&amp;AY28)-2))</f>
@@ -3605,7 +3580,6 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C29:$K29&lt;&gt;"")*(COUNTIFS($C29:$K29,$C29:$K29,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N29" s="5" t="str">
         <f aca="false">IF(LEN(AT29&amp;AU29&amp;AV29&amp;AW29&amp;AX29&amp;AY29)=0,"",LEFT(AT29&amp;AU29&amp;AV29&amp;AW29&amp;AX29&amp;AY29,LEN(AT29&amp;AU29&amp;AV29&amp;AW29&amp;AX29&amp;AY29)-2))</f>
@@ -3699,7 +3673,6 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C30:$K30&lt;&gt;"")*(COUNTIFS($C30:$K30,$C30:$K30,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N30" s="11" t="str">
         <f aca="false">IF(LEN(AT30&amp;AU30&amp;AV30&amp;AW30&amp;AX30&amp;AY30)=0,"",LEFT(AT30&amp;AU30&amp;AV30&amp;AW30&amp;AX30&amp;AY30,LEN(AT30&amp;AU30&amp;AV30&amp;AW30&amp;AX30&amp;AY30)-2))</f>
@@ -3793,7 +3766,6 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C31:$K31&lt;&gt;"")*(COUNTIFS($C31:$K31,$C31:$K31,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N31" s="11" t="str">
         <f aca="false">IF(LEN(AT31&amp;AU31&amp;AV31&amp;AW31&amp;AX31&amp;AY31)=0,"",LEFT(AT31&amp;AU31&amp;AV31&amp;AW31&amp;AX31&amp;AY31,LEN(AT31&amp;AU31&amp;AV31&amp;AW31&amp;AX31&amp;AY31)-2))</f>
@@ -3887,7 +3859,6 @@
       <c r="L32" s="5"/>
       <c r="M32" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C32:$K32&lt;&gt;"")*(COUNTIFS($C32:$K32,$C32:$K32,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N32" s="5" t="str">
         <f aca="false">IF(LEN(AT32&amp;AU32&amp;AV32&amp;AW32&amp;AX32&amp;AY32)=0,"",LEFT(AT32&amp;AU32&amp;AV32&amp;AW32&amp;AX32&amp;AY32,LEN(AT32&amp;AU32&amp;AV32&amp;AW32&amp;AX32&amp;AY32)-2))</f>
@@ -3981,7 +3952,6 @@
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C33:$K33&lt;&gt;"")*(COUNTIFS($C33:$K33,$C33:$K33,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N33" s="5" t="str">
         <f aca="false">IF(LEN(AT33&amp;AU33&amp;AV33&amp;AW33&amp;AX33&amp;AY33)=0,"",LEFT(AT33&amp;AU33&amp;AV33&amp;AW33&amp;AX33&amp;AY33,LEN(AT33&amp;AU33&amp;AV33&amp;AW33&amp;AX33&amp;AY33)-2))</f>
@@ -4075,7 +4045,6 @@
       <c r="L34" s="5"/>
       <c r="M34" s="5" t="str">
         <f aca="false">IF(SUMPRODUCT(($C$3:$K$3&lt;&gt;"")*($C34:$K34&lt;&gt;"")*(COUNTIFS($C34:$K34,$C34:$K34,$C$3:$K$3,$C$3:$K$3)&gt;1))&gt;0,"X","")</f>
-        <v/>
       </c>
       <c r="N34" s="5" t="str">
         <f aca="false">IF(LEN(AT34&amp;AU34&amp;AV34&amp;AW34&amp;AX34&amp;AY34)=0,"",LEFT(AT34&amp;AU34&amp;AV34&amp;AW34&amp;AX34&amp;AY34,LEN(AT34&amp;AU34&amp;AV34&amp;AW34&amp;AX34&amp;AY34)-2))</f>
